--- a/26-2 Sports Day/예산팀/단체티 제작 업체별 견적 비교.xlsx
+++ b/26-2 Sports Day/예산팀/단체티 제작 업체별 견적 비교.xlsx
@@ -511,7 +511,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>9</v>
